--- a/outputs/343-20.xlsx
+++ b/outputs/343-20.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="34">
   <si>
     <t xml:space="preserve">Division</t>
   </si>
@@ -129,9 +129,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -199,17 +200,25 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -404,201 +413,201 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="31.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="31.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="2" t="n">
         <v>44324</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>41770.68</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="2" t="n">
         <v>44205</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>62675.19</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>44587.28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="2" t="n">
         <v>44326</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>74408.01</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="2" t="n">
         <v>44326</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>74408.01</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="2" t="n">
         <v>44540</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>41770.68</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="2" t="n">
         <v>44511</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>94149.37</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D9" s="2" t="n">
         <v>44511</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <v>44587.28</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="2" t="n">
         <v>44511</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <v>56669.01</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="1" t="n">
         <v>90002.26</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D12" s="1"/>
+      <c r="D12" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -616,61 +625,95 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="18.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="18.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.38"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>44324</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>41770.68</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>44540</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>41770.68</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E4" s="1" t="n">
+        <v>44587.28</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>44511</v>
+      </c>
+      <c r="E5" s="1" t="n">
         <v>44587.28</v>
       </c>
     </row>

--- a/outputs/343-20.xlsx
+++ b/outputs/343-20.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="34">
   <si>
     <t xml:space="preserve">Division</t>
   </si>
@@ -129,10 +129,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -200,7 +199,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -215,10 +214,6 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -625,7 +620,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="18.86"/>
@@ -668,52 +663,18 @@
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>44540</v>
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>41770.68</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>44587.28</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>44511</v>
-      </c>
-      <c r="E5" s="1" t="n">
         <v>44587.28</v>
       </c>
     </row>
